--- a/path2shock_calculation/output/path2shock_Down.xlsx
+++ b/path2shock_calculation/output/path2shock_Down.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>13% max</t>
+          <t>(+13 ppts)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>(+1746 ppts)</t>
+          <t>1746.0% max</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -721,12 +721,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>13 peak</t>
+          <t>(+13 ppts)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>(+1764 ppts)</t>
+          <t>1764.0 peak</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -749,12 +749,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>13% peak</t>
+          <t>(+1300 bps)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>(+178200 bps)</t>
+          <t>1782.0 peak</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -777,12 +777,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>13% peak</t>
+          <t>(+1300 bps)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>(+180000 bps)</t>
+          <t>1800.0 peak</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -833,19 +833,19 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1% trough</t>
+          <t>(-500 bps)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>(191400 bps)</t>
+          <t>1900.0 trough</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="F17" t="n">
-        <v>1914</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="18">
@@ -861,19 +861,19 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1% trough</t>
+          <t>(-700 bps)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>(193200 bps)</t>
+          <t>1908.0 trough</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
       <c r="F18" t="n">
-        <v>1932</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="19">
@@ -889,19 +889,19 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1% trough</t>
+          <t>(-3400 bps)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>(195000 bps)</t>
+          <t>1907.0 trough</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>-34</v>
       </c>
       <c r="F19" t="n">
-        <v>1950</v>
+        <v>1907</v>
       </c>
     </row>
     <row r="20">
@@ -939,19 +939,19 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1% trough</t>
+          <t>(-500 bps)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>(198600 bps)</t>
+          <t>1980.0 trough</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="F21" t="n">
-        <v>1986</v>
+        <v>1980</v>
       </c>
     </row>
   </sheetData>

--- a/path2shock_calculation/output/path2shock_Down.xlsx
+++ b/path2shock_calculation/output/path2shock_Down.xlsx
@@ -693,7 +693,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>(+13 ppts)</t>
+          <t>(+13.0 ppts)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
